--- a/artfynd/A 29091-2020 artfynd.xlsx
+++ b/artfynd/A 29091-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29091-2020 artfynd.xlsx
+++ b/artfynd/A 29091-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114461548</v>
+        <v>116132149</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
+        <v>104820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrvallsmossen, Upl</t>
+          <t>Norrvallsmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619064</v>
+        <v>618983</v>
       </c>
       <c r="R3" t="n">
-        <v>6662190</v>
+        <v>6662174</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,19 +859,29 @@
           <t>Harbo</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>C-Heb-0250</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fem skott</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,32 +890,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116132149</v>
+        <v>116131937</v>
       </c>
       <c r="B4" t="n">
-        <v>104820</v>
+        <v>97733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -992,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fem skott</t>
+          <t>Ett 50-tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,128 +1028,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>116131937</v>
-      </c>
-      <c r="B5" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Norrvallsmossen, norr om, Upl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>618983</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6662174</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Harbo</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett 50-tal bladrosetter.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
